--- a/RDDT_Model.xlsx
+++ b/RDDT_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Communication Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25074DB0-F58B-4F6F-AB7C-F3F5C634772B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3643B932-961D-4237-812A-BE5E483CFD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="2565" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1961,10 +1961,10 @@
     <t>Registered Exchange: NYSE</t>
   </si>
   <si>
-    <t>10/31/25</t>
-  </si>
-  <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -11198,10 +11198,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="44">
-        <v>208.95</v>
+        <v>244.97</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="2:19">
@@ -11212,7 +11212,7 @@
         <v>188.041</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="2:19">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C5" s="61">
         <f>C3*C4</f>
-        <v>39291.166949999999</v>
+        <v>46064.403769999997</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -11233,7 +11233,7 @@
         <v>2225.8200000000002</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -11245,7 +11245,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="C8" s="62">
         <f>C5-C6+C7</f>
-        <v>37065.346949999999</v>
+        <v>43838.583769999997</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="15">
@@ -11486,9 +11486,6 @@
     <hyperlink ref="S15" r:id="rId3" xr:uid="{FA01A2D0-92F9-4840-9CF3-8CB64E42789D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
@@ -11880,43 +11877,43 @@
       </c>
       <c r="Y4" s="72">
         <f t="shared" ref="Y4:AH4" si="2">X4*(1+Y8)</f>
-        <v>2050.8388799999998</v>
+        <v>2086.40256</v>
       </c>
       <c r="Z4" s="72">
         <f t="shared" si="2"/>
-        <v>2973.7163759999994</v>
+        <v>3025.2837119999999</v>
       </c>
       <c r="AA4" s="72">
         <f t="shared" si="2"/>
-        <v>3925.3056163199994</v>
+        <v>3993.3744998400002</v>
       </c>
       <c r="AB4" s="72">
         <f t="shared" si="2"/>
-        <v>4985.1381327263998</v>
+        <v>5071.5856147968007</v>
       </c>
       <c r="AC4" s="72">
         <f t="shared" si="2"/>
-        <v>6081.8685219262079</v>
+        <v>6187.3344500520971</v>
       </c>
       <c r="AD4" s="72">
         <f t="shared" si="2"/>
-        <v>7176.6048558729253</v>
+        <v>7301.054651061474</v>
       </c>
       <c r="AE4" s="72">
         <f t="shared" si="2"/>
-        <v>8324.8616328125936</v>
+        <v>8469.223395231309</v>
       </c>
       <c r="AF4" s="72">
         <f t="shared" si="2"/>
-        <v>9615.2151858985453</v>
+        <v>9781.9530214921615</v>
       </c>
       <c r="AG4" s="72">
         <f t="shared" si="2"/>
-        <v>11009.421387853834</v>
+        <v>11200.336209608526</v>
       </c>
       <c r="AH4" s="72">
         <f t="shared" si="2"/>
-        <v>12550.740382153372</v>
+        <v>12768.383278953721</v>
       </c>
     </row>
     <row r="5" spans="2:87">
@@ -11972,39 +11969,39 @@
       </c>
       <c r="Z5" s="72">
         <f t="shared" si="3"/>
-        <v>166.27130099999999</v>
+        <v>169.1629758</v>
       </c>
       <c r="AA5" s="72">
         <f t="shared" si="3"/>
-        <v>184.56114411000001</v>
+        <v>191.15416265399998</v>
       </c>
       <c r="AB5" s="72">
         <f t="shared" si="3"/>
-        <v>201.17164707990003</v>
+        <v>212.18112054593999</v>
       </c>
       <c r="AC5" s="72">
         <f t="shared" si="3"/>
-        <v>217.26537884629204</v>
+        <v>231.27742139507461</v>
       </c>
       <c r="AD5" s="72">
         <f t="shared" si="3"/>
-        <v>232.4739553655325</v>
+        <v>249.77961510668061</v>
       </c>
       <c r="AE5" s="72">
         <f t="shared" si="3"/>
-        <v>246.42239268746448</v>
+        <v>267.26418816414827</v>
       </c>
       <c r="AF5" s="72">
         <f t="shared" si="3"/>
-        <v>258.74351232183773</v>
+        <v>283.30003945399716</v>
       </c>
       <c r="AG5" s="72">
         <f t="shared" si="3"/>
-        <v>269.09325281471126</v>
+        <v>297.46504142669704</v>
       </c>
       <c r="AH5" s="72">
         <f t="shared" si="3"/>
-        <v>277.1660503991526</v>
+        <v>309.36364308376494</v>
       </c>
     </row>
     <row r="6" spans="2:87" s="2" customFormat="1" ht="15">
@@ -12070,43 +12067,43 @@
       </c>
       <c r="Y6" s="73">
         <f t="shared" ref="Y6:AH6" si="7">SUM(Y4:Y5)</f>
-        <v>2195.4226199999998</v>
+        <v>2230.9863</v>
       </c>
       <c r="Z6" s="73">
         <f t="shared" si="7"/>
-        <v>3139.9876769999992</v>
+        <v>3194.4466877999998</v>
       </c>
       <c r="AA6" s="73">
         <f t="shared" si="7"/>
-        <v>4109.8667604299999</v>
+        <v>4184.5286624939999</v>
       </c>
       <c r="AB6" s="73">
         <f t="shared" si="7"/>
-        <v>5186.3097798063</v>
+        <v>5283.7667353427405</v>
       </c>
       <c r="AC6" s="73">
         <f t="shared" si="7"/>
-        <v>6299.1339007725001</v>
+        <v>6418.6118714471713</v>
       </c>
       <c r="AD6" s="73">
         <f t="shared" si="7"/>
-        <v>7409.078811238458</v>
+        <v>7550.8342661681545</v>
       </c>
       <c r="AE6" s="73">
         <f t="shared" si="7"/>
-        <v>8571.2840255000574</v>
+        <v>8736.4875833954575</v>
       </c>
       <c r="AF6" s="73">
         <f t="shared" si="7"/>
-        <v>9873.9586982203837</v>
+        <v>10065.253060946159</v>
       </c>
       <c r="AG6" s="73">
         <f t="shared" si="7"/>
-        <v>11278.514640668545</v>
+        <v>11497.801251035222</v>
       </c>
       <c r="AH6" s="73">
         <f t="shared" si="7"/>
-        <v>12827.906432552525</v>
+        <v>13077.746922037486</v>
       </c>
       <c r="AI6" s="34"/>
       <c r="AJ6" s="34"/>
@@ -12211,7 +12208,7 @@
         <v>0.50289433582409315</v>
       </c>
       <c r="Y8" s="80">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="Z8" s="80">
         <v>0.45</v>
@@ -12281,31 +12278,31 @@
         <v>0.26</v>
       </c>
       <c r="Z9" s="80">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AA9" s="80">
+        <v>0.13</v>
+      </c>
+      <c r="AB9" s="80">
         <v>0.11</v>
       </c>
-      <c r="AB9" s="80">
+      <c r="AC9" s="80">
         <v>0.09</v>
       </c>
-      <c r="AC9" s="80">
+      <c r="AD9" s="80">
         <v>0.08</v>
       </c>
-      <c r="AD9" s="80">
+      <c r="AE9" s="80">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE9" s="80">
+      <c r="AF9" s="80">
         <v>0.06</v>
       </c>
-      <c r="AF9" s="80">
+      <c r="AG9" s="80">
         <v>0.05</v>
       </c>
-      <c r="AG9" s="80">
+      <c r="AH9" s="80">
         <v>0.04</v>
-      </c>
-      <c r="AH9" s="80">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="2:87" s="2" customFormat="1" ht="15">
@@ -12351,43 +12348,43 @@
       </c>
       <c r="Y10" s="81">
         <f t="shared" si="12"/>
-        <v>0.6885203640964308</v>
+        <v>0.7158727277621606</v>
       </c>
       <c r="Z10" s="81">
         <f t="shared" si="12"/>
-        <v>0.43024292835244604</v>
+        <v>0.43185401353652408</v>
       </c>
       <c r="AA10" s="81">
         <f t="shared" si="12"/>
-        <v>0.30887990119650421</v>
+        <v>0.30993848746177233</v>
       </c>
       <c r="AB10" s="81">
         <f t="shared" si="12"/>
-        <v>0.26191676813962594</v>
+        <v>0.26269101289739738</v>
       </c>
       <c r="AC10" s="81">
         <f t="shared" si="12"/>
-        <v>0.21456954331944322</v>
+        <v>0.21477956786273933</v>
       </c>
       <c r="AD10" s="81">
         <f t="shared" si="12"/>
-        <v>0.17620595592194643</v>
+        <v>0.17639676886487088</v>
       </c>
       <c r="AE10" s="81">
         <f t="shared" si="12"/>
-        <v>0.15686230958951453</v>
+        <v>0.15702282362886377</v>
       </c>
       <c r="AF10" s="81">
         <f t="shared" si="12"/>
-        <v>0.15198127478272738</v>
+        <v>0.15209378653226158</v>
       </c>
       <c r="AG10" s="81">
         <f t="shared" si="12"/>
-        <v>0.14224851302054864</v>
+        <v>0.14232609765644577</v>
       </c>
       <c r="AH10" s="81">
         <f t="shared" si="12"/>
-        <v>0.1373755180755023</v>
+        <v>0.13741285281479465</v>
       </c>
       <c r="AI10" s="34"/>
       <c r="AJ10" s="34"/>
@@ -13727,43 +13724,43 @@
       </c>
       <c r="Y35" s="73">
         <f>Y6</f>
-        <v>2195.4226199999998</v>
+        <v>2230.9863</v>
       </c>
       <c r="Z35" s="73">
         <f t="shared" ref="Z35:AH35" si="38">Z6</f>
-        <v>3139.9876769999992</v>
+        <v>3194.4466877999998</v>
       </c>
       <c r="AA35" s="73">
         <f t="shared" si="38"/>
-        <v>4109.8667604299999</v>
+        <v>4184.5286624939999</v>
       </c>
       <c r="AB35" s="73">
         <f t="shared" si="38"/>
-        <v>5186.3097798063</v>
+        <v>5283.7667353427405</v>
       </c>
       <c r="AC35" s="73">
         <f t="shared" si="38"/>
-        <v>6299.1339007725001</v>
+        <v>6418.6118714471713</v>
       </c>
       <c r="AD35" s="73">
         <f t="shared" si="38"/>
-        <v>7409.078811238458</v>
+        <v>7550.8342661681545</v>
       </c>
       <c r="AE35" s="73">
         <f t="shared" si="38"/>
-        <v>8571.2840255000574</v>
+        <v>8736.4875833954575</v>
       </c>
       <c r="AF35" s="73">
         <f t="shared" si="38"/>
-        <v>9873.9586982203837</v>
+        <v>10065.253060946159</v>
       </c>
       <c r="AG35" s="73">
         <f t="shared" si="38"/>
-        <v>11278.514640668545</v>
+        <v>11497.801251035222</v>
       </c>
       <c r="AH35" s="73">
         <f t="shared" si="38"/>
-        <v>12827.906432552525</v>
+        <v>13077.746922037486</v>
       </c>
       <c r="AI35" s="73"/>
       <c r="AJ35" s="73"/>
@@ -13867,43 +13864,43 @@
       </c>
       <c r="Y36" s="72">
         <f>Y35*(1-Y49)</f>
-        <v>208.69267440049808</v>
+        <v>212.07328978776394</v>
       </c>
       <c r="Z36" s="72">
         <f t="shared" ref="Z36:AH36" si="39">Z35*(1-Z49)</f>
-        <v>282.59889092999981</v>
+        <v>287.5002019019999</v>
       </c>
       <c r="AA36" s="72">
         <f t="shared" si="39"/>
-        <v>359.6133415376251</v>
+        <v>366.14625796822509</v>
       </c>
       <c r="AB36" s="72">
         <f t="shared" si="39"/>
-        <v>440.83633128353529</v>
+        <v>449.12017250413277</v>
       </c>
       <c r="AC36" s="72">
         <f t="shared" si="39"/>
-        <v>503.93071206179974</v>
+        <v>513.4889497157734</v>
       </c>
       <c r="AD36" s="72">
         <f t="shared" si="39"/>
-        <v>585.31722608783787</v>
+        <v>596.5159070272839</v>
       </c>
       <c r="AE36" s="72">
         <f t="shared" si="39"/>
-        <v>668.56015398900411</v>
+        <v>681.44603150484534</v>
       </c>
       <c r="AF36" s="72">
         <f t="shared" si="39"/>
-        <v>760.29481976296915</v>
+        <v>775.02448569285377</v>
       </c>
       <c r="AG36" s="72">
         <f t="shared" si="39"/>
-        <v>857.16711269080895</v>
+        <v>873.83289507867642</v>
       </c>
       <c r="AH36" s="72">
         <f t="shared" si="39"/>
-        <v>962.09298244143883</v>
+        <v>980.83101915281088</v>
       </c>
       <c r="AI36" s="72"/>
       <c r="AJ36" s="72"/>
@@ -14014,43 +14011,43 @@
       </c>
       <c r="Y37" s="72">
         <f>Y35-Y36</f>
-        <v>1986.7299455995017</v>
+        <v>2018.913010212236</v>
       </c>
       <c r="Z37" s="72">
         <f t="shared" ref="Z37:AH37" si="41">Z35-Z36</f>
-        <v>2857.3887860699992</v>
+        <v>2906.946485898</v>
       </c>
       <c r="AA37" s="72">
         <f t="shared" si="41"/>
-        <v>3750.2534188923746</v>
+        <v>3818.3824045257747</v>
       </c>
       <c r="AB37" s="72">
         <f t="shared" si="41"/>
-        <v>4745.4734485227646</v>
+        <v>4834.6465628386077</v>
       </c>
       <c r="AC37" s="72">
         <f t="shared" si="41"/>
-        <v>5795.2031887107005</v>
+        <v>5905.1229217313976</v>
       </c>
       <c r="AD37" s="72">
         <f t="shared" si="41"/>
-        <v>6823.7615851506198</v>
+        <v>6954.3183591408706</v>
       </c>
       <c r="AE37" s="72">
         <f t="shared" si="41"/>
-        <v>7902.7238715110534</v>
+        <v>8055.041551890612</v>
       </c>
       <c r="AF37" s="72">
         <f t="shared" si="41"/>
-        <v>9113.6638784574152</v>
+        <v>9290.2285752533062</v>
       </c>
       <c r="AG37" s="72">
         <f t="shared" si="41"/>
-        <v>10421.347527977736</v>
+        <v>10623.968355956546</v>
       </c>
       <c r="AH37" s="72">
         <f t="shared" si="41"/>
-        <v>11865.813450111087</v>
+        <v>12096.915902884675</v>
       </c>
       <c r="AI37" s="72"/>
       <c r="AJ37" s="72"/>
@@ -14153,43 +14150,43 @@
       </c>
       <c r="Y38" s="72">
         <f>Y35*Y50</f>
-        <v>724.48946460000002</v>
+        <v>870.08465699999999</v>
       </c>
       <c r="Z38" s="72">
         <f t="shared" ref="Z38:AH38" si="42">Z35*Z50</f>
-        <v>879.19654955999988</v>
+        <v>926.3895394619999</v>
       </c>
       <c r="AA38" s="72">
         <f t="shared" si="42"/>
-        <v>1027.4666901075</v>
+        <v>1087.9774522484399</v>
       </c>
       <c r="AB38" s="72">
         <f t="shared" si="42"/>
-        <v>1192.851249355449</v>
+        <v>1215.2663491288304</v>
       </c>
       <c r="AC38" s="72">
         <f t="shared" si="42"/>
-        <v>1322.818119162225</v>
+        <v>1347.908493003906</v>
       </c>
       <c r="AD38" s="72">
         <f t="shared" si="42"/>
-        <v>1333.6341860229224</v>
+        <v>1359.1501679102678</v>
       </c>
       <c r="AE38" s="72">
         <f t="shared" si="42"/>
-        <v>1371.4054440800091</v>
+        <v>1397.8380133432731</v>
       </c>
       <c r="AF38" s="72">
         <f t="shared" si="42"/>
-        <v>1481.0938047330576</v>
+        <v>1509.7879591419239</v>
       </c>
       <c r="AG38" s="72">
         <f t="shared" si="42"/>
-        <v>1578.9920496935965</v>
+        <v>1609.6921751449313</v>
       </c>
       <c r="AH38" s="72">
         <f t="shared" si="42"/>
-        <v>1667.6278362318283</v>
+        <v>1700.1070998648731</v>
       </c>
       <c r="AI38" s="72"/>
       <c r="AJ38" s="72"/>
@@ -14292,43 +14289,43 @@
       </c>
       <c r="Y39" s="72">
         <f>Y35*Y51</f>
-        <v>472.01586329999998</v>
+        <v>479.66205450000001</v>
       </c>
       <c r="Z39" s="72">
         <f t="shared" ref="Z39:AH39" si="43">Z35*Z51</f>
-        <v>847.79667278999977</v>
+        <v>862.50060570599999</v>
       </c>
       <c r="AA39" s="72">
         <f t="shared" si="43"/>
-        <v>1109.6640253161002</v>
+        <v>1129.8227388733801</v>
       </c>
       <c r="AB39" s="72">
         <f t="shared" si="43"/>
-        <v>1400.303640547701</v>
+        <v>1426.6170185425401</v>
       </c>
       <c r="AC39" s="72">
         <f t="shared" si="43"/>
-        <v>1700.7661532085751</v>
+        <v>1733.0252052907363</v>
       </c>
       <c r="AD39" s="72">
         <f t="shared" si="43"/>
-        <v>2000.4512790343838</v>
+        <v>2038.7252518654018</v>
       </c>
       <c r="AE39" s="72">
         <f t="shared" si="43"/>
-        <v>2314.2466868850156</v>
+        <v>2358.8516475167735</v>
       </c>
       <c r="AF39" s="72">
         <f t="shared" si="43"/>
-        <v>2665.9688485195038</v>
+        <v>2717.6183264554634</v>
       </c>
       <c r="AG39" s="72">
         <f t="shared" si="43"/>
-        <v>3045.1989529805073</v>
+        <v>3104.4063377795101</v>
       </c>
       <c r="AH39" s="72">
         <f t="shared" si="43"/>
-        <v>3463.5347367891818</v>
+        <v>3530.9916689501215</v>
       </c>
       <c r="AI39" s="72"/>
       <c r="AJ39" s="72"/>
@@ -14430,43 +14427,43 @@
       </c>
       <c r="Y40" s="72">
         <f>Y35*Y52</f>
-        <v>702.53523839999991</v>
+        <v>713.915616</v>
       </c>
       <c r="Z40" s="72">
         <f t="shared" ref="Z40:AH40" si="44">Z35*Z52</f>
-        <v>1004.7960566399997</v>
+        <v>1022.222940096</v>
       </c>
       <c r="AA40" s="72">
         <f t="shared" si="44"/>
-        <v>1315.1573633375999</v>
+        <v>1339.0491719980801</v>
       </c>
       <c r="AB40" s="72">
         <f t="shared" si="44"/>
-        <v>1659.6191295380161</v>
+        <v>1690.805355309677</v>
       </c>
       <c r="AC40" s="72">
         <f t="shared" si="44"/>
-        <v>2015.7228482472001</v>
+        <v>2053.955798863095</v>
       </c>
       <c r="AD40" s="72">
         <f t="shared" si="44"/>
-        <v>2370.9052195963068</v>
+        <v>2416.2669651738097</v>
       </c>
       <c r="AE40" s="72">
         <f t="shared" si="44"/>
-        <v>2742.8108881600183</v>
+        <v>2795.6760266865463</v>
       </c>
       <c r="AF40" s="72">
         <f t="shared" si="44"/>
-        <v>3159.6667834305226</v>
+        <v>3220.880979502771</v>
       </c>
       <c r="AG40" s="72">
         <f t="shared" si="44"/>
-        <v>3609.1246850139346</v>
+        <v>3679.2964003312709</v>
       </c>
       <c r="AH40" s="72">
         <f t="shared" si="44"/>
-        <v>4104.9300584168077</v>
+        <v>4184.8790150519953</v>
       </c>
       <c r="AI40" s="72"/>
       <c r="AJ40" s="72"/>
@@ -14577,43 +14574,43 @@
       </c>
       <c r="Y41" s="72">
         <f>Y37-SUM(Y38:Y40)</f>
-        <v>87.689379299501979</v>
+        <v>-44.749317287764143</v>
       </c>
       <c r="Z41" s="72">
         <f t="shared" ref="Z41:AH41" si="47">Z37-SUM(Z38:Z40)</f>
-        <v>125.59950707999997</v>
+        <v>95.8334006340001</v>
       </c>
       <c r="AA41" s="72">
         <f t="shared" si="47"/>
-        <v>297.96534013117434</v>
+        <v>261.53304140587488</v>
       </c>
       <c r="AB41" s="72">
         <f t="shared" si="47"/>
-        <v>492.69942908159828</v>
+        <v>501.95783985756043</v>
       </c>
       <c r="AC41" s="72">
         <f t="shared" si="47"/>
-        <v>755.89606809270026</v>
+        <v>770.23342457366016</v>
       </c>
       <c r="AD41" s="72">
         <f t="shared" si="47"/>
-        <v>1118.7709004970066</v>
+        <v>1140.1759741913911</v>
       </c>
       <c r="AE41" s="72">
         <f t="shared" si="47"/>
-        <v>1474.2608523860099</v>
+        <v>1502.6758643440189</v>
       </c>
       <c r="AF41" s="72">
         <f t="shared" si="47"/>
-        <v>1806.9344417743314</v>
+        <v>1841.9413101531482</v>
       </c>
       <c r="AG41" s="72">
         <f t="shared" si="47"/>
-        <v>2188.0318402896974</v>
+        <v>2230.5734427008319</v>
       </c>
       <c r="AH41" s="72">
         <f t="shared" si="47"/>
-        <v>2629.7208186732696</v>
+        <v>2680.9381190176846</v>
       </c>
       <c r="AI41" s="72"/>
       <c r="AJ41" s="72"/>
@@ -14719,39 +14716,39 @@
       </c>
       <c r="Z42" s="72">
         <f>Y57*($AH$59)</f>
-        <v>947.4168952037985</v>
+        <v>1588.5871684140411</v>
       </c>
       <c r="AA42" s="72">
         <f t="shared" ref="AA42:AH42" si="48">Z57*($AH$59)</f>
-        <v>1554.314972335515</v>
+        <v>2541.2954422676135</v>
       </c>
       <c r="AB42" s="72">
         <f t="shared" si="48"/>
-        <v>2539.7280985677939</v>
+        <v>4032.400195581909</v>
       </c>
       <c r="AC42" s="72">
         <f t="shared" si="48"/>
-        <v>4152.9795432772707</v>
+        <v>6444.6786704357064</v>
       </c>
       <c r="AD42" s="72">
         <f t="shared" si="48"/>
-        <v>6764.5013685260965</v>
+        <v>10283.011904980689</v>
       </c>
       <c r="AE42" s="72">
         <f t="shared" si="48"/>
-        <v>10958.402215646387</v>
+        <v>16360.147856700238</v>
       </c>
       <c r="AF42" s="72">
         <f t="shared" si="48"/>
-        <v>17572.578967839625</v>
+        <v>25863.170076295784</v>
       </c>
       <c r="AG42" s="72">
         <f t="shared" si="48"/>
-        <v>27882.480101754252</v>
+        <v>40602.28933388662</v>
       </c>
       <c r="AH42" s="72">
         <f t="shared" si="48"/>
-        <v>43879.99245492163</v>
+        <v>63389.372331031147</v>
       </c>
       <c r="AI42" s="72"/>
       <c r="AJ42" s="72"/>
@@ -14862,43 +14859,43 @@
       </c>
       <c r="Y43" s="72">
         <f>Y41+Y42</f>
-        <v>1118.5384992995021</v>
+        <v>986.09980271223594</v>
       </c>
       <c r="Z43" s="72">
         <f t="shared" ref="Z43:AH43" si="51">Z41+Z42</f>
-        <v>1073.0164022837985</v>
+        <v>1684.4205690480412</v>
       </c>
       <c r="AA43" s="72">
         <f t="shared" si="51"/>
-        <v>1852.2803124666893</v>
+        <v>2802.8284836734883</v>
       </c>
       <c r="AB43" s="72">
         <f t="shared" si="51"/>
-        <v>3032.4275276493922</v>
+        <v>4534.3580354394689</v>
       </c>
       <c r="AC43" s="72">
         <f t="shared" si="51"/>
-        <v>4908.875611369971</v>
+        <v>7214.9120950093666</v>
       </c>
       <c r="AD43" s="72">
         <f t="shared" si="51"/>
-        <v>7883.272269023103</v>
+        <v>11423.187879172081</v>
       </c>
       <c r="AE43" s="72">
         <f t="shared" si="51"/>
-        <v>12432.663068032398</v>
+        <v>17862.823721044257</v>
       </c>
       <c r="AF43" s="72">
         <f t="shared" si="51"/>
-        <v>19379.513409613955</v>
+        <v>27705.111386448931</v>
       </c>
       <c r="AG43" s="72">
         <f t="shared" si="51"/>
-        <v>30070.511942043951</v>
+        <v>42832.862776587455</v>
       </c>
       <c r="AH43" s="72">
         <f t="shared" si="51"/>
-        <v>46509.713273594898</v>
+        <v>66070.310450048826</v>
       </c>
       <c r="AI43" s="72"/>
       <c r="AJ43" s="72"/>
@@ -15000,43 +14997,43 @@
       </c>
       <c r="Y44" s="72">
         <f>Y43*Y54</f>
-        <v>-11.18538499299502</v>
+        <v>-9.8609980271223598</v>
       </c>
       <c r="Z44" s="72">
         <f t="shared" ref="Z44:AH44" si="52">Z43*Z54</f>
-        <v>-10.730164022837984</v>
+        <v>-16.844205690480411</v>
       </c>
       <c r="AA44" s="72">
         <f t="shared" si="52"/>
-        <v>92.614015623334467</v>
+        <v>140.14142418367442</v>
       </c>
       <c r="AB44" s="72">
         <f t="shared" si="52"/>
-        <v>151.62137638246961</v>
+        <v>226.71790177197346</v>
       </c>
       <c r="AC44" s="72">
         <f t="shared" si="52"/>
-        <v>245.44378056849857</v>
+        <v>360.74560475046837</v>
       </c>
       <c r="AD44" s="72">
         <f t="shared" si="52"/>
-        <v>394.16361345115519</v>
+        <v>571.15939395860403</v>
       </c>
       <c r="AE44" s="72">
         <f t="shared" si="52"/>
-        <v>621.63315340161989</v>
+        <v>893.1411860522129</v>
       </c>
       <c r="AF44" s="72">
         <f t="shared" si="52"/>
-        <v>968.97567048069777</v>
+        <v>1385.2555693224467</v>
       </c>
       <c r="AG44" s="72">
         <f t="shared" si="52"/>
-        <v>1503.5255971021977</v>
+        <v>2141.6431388293727</v>
       </c>
       <c r="AH44" s="72">
         <f t="shared" si="52"/>
-        <v>2325.4856636797449</v>
+        <v>3303.5155225024414</v>
       </c>
       <c r="AI44" s="72"/>
       <c r="AJ44" s="72"/>
@@ -15152,243 +15149,243 @@
       </c>
       <c r="Y45" s="73">
         <f>Y43-Y44</f>
-        <v>1129.7238842924971</v>
+        <v>995.96080073935832</v>
       </c>
       <c r="Z45" s="73">
         <f t="shared" ref="Z45:AH45" si="55">Z43-Z44</f>
-        <v>1083.7465663066364</v>
+        <v>1701.2647747385217</v>
       </c>
       <c r="AA45" s="73">
         <f t="shared" si="55"/>
-        <v>1759.6662968433548</v>
+        <v>2662.6870594898137</v>
       </c>
       <c r="AB45" s="73">
         <f t="shared" si="55"/>
-        <v>2880.8061512669228</v>
+        <v>4307.6401336674953</v>
       </c>
       <c r="AC45" s="73">
         <f t="shared" si="55"/>
-        <v>4663.4318308014726</v>
+        <v>6854.1664902588982</v>
       </c>
       <c r="AD45" s="73">
         <f t="shared" si="55"/>
-        <v>7489.1086555719476</v>
+        <v>10852.028485213477</v>
       </c>
       <c r="AE45" s="73">
         <f t="shared" si="55"/>
-        <v>11811.029914630777</v>
+        <v>16969.682534992044</v>
       </c>
       <c r="AF45" s="73">
         <f t="shared" si="55"/>
-        <v>18410.537739133259</v>
+        <v>26319.855817126485</v>
       </c>
       <c r="AG45" s="73">
         <f t="shared" si="55"/>
-        <v>28566.986344941753</v>
+        <v>40691.219637758084</v>
       </c>
       <c r="AH45" s="73">
         <f t="shared" si="55"/>
-        <v>44184.22760991515</v>
+        <v>62766.794927546383</v>
       </c>
       <c r="AI45" s="73">
         <f>AH45*(1+$AH$60)</f>
-        <v>45178.372731138239</v>
+        <v>64179.047813416175</v>
       </c>
       <c r="AJ45" s="73">
         <f t="shared" ref="AJ45:CF45" si="56">AI45*(1+$AH$60)</f>
-        <v>46194.886117588845</v>
+        <v>65623.07638921804</v>
       </c>
       <c r="AK45" s="73">
         <f t="shared" si="56"/>
-        <v>47234.271055234589</v>
+        <v>67099.59560797544</v>
       </c>
       <c r="AL45" s="73">
         <f t="shared" si="56"/>
-        <v>48297.042153977367</v>
+        <v>68609.336509154891</v>
       </c>
       <c r="AM45" s="73">
         <f t="shared" si="56"/>
-        <v>49383.725602441853</v>
+        <v>70153.04658061087</v>
       </c>
       <c r="AN45" s="73">
         <f t="shared" si="56"/>
-        <v>50494.859428496791</v>
+        <v>71731.490128674617</v>
       </c>
       <c r="AO45" s="73">
         <f t="shared" si="56"/>
-        <v>51630.99376563797</v>
+        <v>73345.448656569788</v>
       </c>
       <c r="AP45" s="73">
         <f t="shared" si="56"/>
-        <v>52792.691125364821</v>
+        <v>74995.721251342606</v>
       </c>
       <c r="AQ45" s="73">
         <f t="shared" si="56"/>
-        <v>53980.526675685527</v>
+        <v>76683.124979497807</v>
       </c>
       <c r="AR45" s="73">
         <f t="shared" si="56"/>
-        <v>55195.088525888452</v>
+        <v>78408.495291536499</v>
       </c>
       <c r="AS45" s="73">
         <f t="shared" si="56"/>
-        <v>56436.97801772094</v>
+        <v>80172.686435596072</v>
       </c>
       <c r="AT45" s="73">
         <f t="shared" si="56"/>
-        <v>57706.810023119659</v>
+        <v>81976.571880396979</v>
       </c>
       <c r="AU45" s="73">
         <f t="shared" si="56"/>
-        <v>59005.213248639848</v>
+        <v>83821.044747705906</v>
       </c>
       <c r="AV45" s="73">
         <f t="shared" si="56"/>
-        <v>60332.830546734243</v>
+        <v>85707.018254529292</v>
       </c>
       <c r="AW45" s="73">
         <f t="shared" si="56"/>
-        <v>61690.319234035764</v>
+        <v>87635.426165256198</v>
       </c>
       <c r="AX45" s="73">
         <f t="shared" si="56"/>
-        <v>63078.351416801568</v>
+        <v>89607.223253974458</v>
       </c>
       <c r="AY45" s="73">
         <f t="shared" si="56"/>
-        <v>64497.614323679598</v>
+        <v>91623.385777188887</v>
       </c>
       <c r="AZ45" s="73">
         <f t="shared" si="56"/>
-        <v>65948.810645962381</v>
+        <v>93684.911957175631</v>
       </c>
       <c r="BA45" s="73">
         <f t="shared" si="56"/>
-        <v>67432.658885496538</v>
+        <v>95792.822476212081</v>
       </c>
       <c r="BB45" s="73">
         <f t="shared" si="56"/>
-        <v>68949.893710420205</v>
+        <v>97948.160981926849</v>
       </c>
       <c r="BC45" s="73">
         <f t="shared" si="56"/>
-        <v>70501.266318904658</v>
+        <v>100151.9946040202</v>
       </c>
       <c r="BD45" s="73">
         <f t="shared" si="56"/>
-        <v>72087.544811080006</v>
+        <v>102405.41448261065</v>
       </c>
       <c r="BE45" s="73">
         <f t="shared" si="56"/>
-        <v>73709.514569329302</v>
+        <v>104709.53630846938</v>
       </c>
       <c r="BF45" s="73">
         <f t="shared" si="56"/>
-        <v>75367.978647139214</v>
+        <v>107065.50087540994</v>
       </c>
       <c r="BG45" s="73">
         <f t="shared" si="56"/>
-        <v>77063.758166699845</v>
+        <v>109474.47464510666</v>
       </c>
       <c r="BH45" s="73">
         <f t="shared" si="56"/>
-        <v>78797.692725450586</v>
+        <v>111937.65032462156</v>
       </c>
       <c r="BI45" s="73">
         <f t="shared" si="56"/>
-        <v>80570.640811773221</v>
+        <v>114456.24745692554</v>
       </c>
       <c r="BJ45" s="73">
         <f t="shared" si="56"/>
-        <v>82383.480230038112</v>
+        <v>117031.51302470636</v>
       </c>
       <c r="BK45" s="73">
         <f t="shared" si="56"/>
-        <v>84237.108535213963</v>
+        <v>119664.72206776225</v>
       </c>
       <c r="BL45" s="73">
         <f t="shared" si="56"/>
-        <v>86132.443477256282</v>
+        <v>122357.1783142869</v>
       </c>
       <c r="BM45" s="73">
         <f t="shared" si="56"/>
-        <v>88070.423455494543</v>
+        <v>125110.21482635835</v>
       </c>
       <c r="BN45" s="73">
         <f t="shared" si="56"/>
-        <v>90052.007983243166</v>
+        <v>127925.1946599514</v>
       </c>
       <c r="BO45" s="73">
         <f t="shared" si="56"/>
-        <v>92078.178162866127</v>
+        <v>130803.51153980031</v>
       </c>
       <c r="BP45" s="73">
         <f t="shared" si="56"/>
-        <v>94149.937171530604</v>
+        <v>133746.59054944583</v>
       </c>
       <c r="BQ45" s="73">
         <f t="shared" si="56"/>
-        <v>96268.310757890038</v>
+        <v>136755.88883680836</v>
       </c>
       <c r="BR45" s="73">
         <f t="shared" si="56"/>
-        <v>98434.347749942564</v>
+        <v>139832.89633563653</v>
       </c>
       <c r="BS45" s="73">
         <f t="shared" si="56"/>
-        <v>100649.12057431627</v>
+        <v>142979.13650318835</v>
       </c>
       <c r="BT45" s="73">
         <f t="shared" si="56"/>
-        <v>102913.72578723838</v>
+        <v>146196.16707451007</v>
       </c>
       <c r="BU45" s="73">
         <f t="shared" si="56"/>
-        <v>105229.28461745124</v>
+        <v>149485.58083368654</v>
       </c>
       <c r="BV45" s="73">
         <f t="shared" si="56"/>
-        <v>107596.94352134388</v>
+        <v>152849.00640244447</v>
       </c>
       <c r="BW45" s="73">
         <f t="shared" si="56"/>
-        <v>110017.87475057412</v>
+        <v>156288.10904649948</v>
       </c>
       <c r="BX45" s="73">
         <f t="shared" si="56"/>
-        <v>112493.27693246203</v>
+        <v>159804.5915000457</v>
       </c>
       <c r="BY45" s="73">
         <f t="shared" si="56"/>
-        <v>115024.37566344242</v>
+        <v>163400.19480879672</v>
       </c>
       <c r="BZ45" s="73">
         <f t="shared" si="56"/>
-        <v>117612.42411586987</v>
+        <v>167076.69919199464</v>
       </c>
       <c r="CA45" s="73">
         <f t="shared" si="56"/>
-        <v>120258.70365847694</v>
+        <v>170835.92492381451</v>
       </c>
       <c r="CB45" s="73">
         <f t="shared" si="56"/>
-        <v>122964.52449079267</v>
+        <v>174679.73323460034</v>
       </c>
       <c r="CC45" s="73">
         <f t="shared" si="56"/>
-        <v>125731.2262918355</v>
+        <v>178610.02723237884</v>
       </c>
       <c r="CD45" s="73">
         <f t="shared" si="56"/>
-        <v>128560.17888340179</v>
+        <v>182628.75284510734</v>
       </c>
       <c r="CE45" s="73">
         <f t="shared" si="56"/>
-        <v>131452.78290827834</v>
+        <v>186737.89978412224</v>
       </c>
       <c r="CF45" s="73">
         <f t="shared" si="56"/>
-        <v>134410.47052371461</v>
+        <v>190939.50252926498</v>
       </c>
       <c r="CG45" s="34"/>
       <c r="CH45" s="34"/>
@@ -15660,13 +15657,13 @@
         <v>0.71923427459516009</v>
       </c>
       <c r="Y50" s="82">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="Z50" s="82">
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA50" s="82">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AB50" s="82">
         <v>0.23</v>
@@ -15922,43 +15919,43 @@
       </c>
       <c r="Y53" s="82">
         <f>Y42/Y35</f>
-        <v>0.46954472938791175</v>
+        <v>0.46205981632428672</v>
       </c>
       <c r="Z53" s="82">
         <f t="shared" ref="Z53:AH53" si="71">Z42/Z35</f>
-        <v>0.30172630999271238</v>
+        <v>0.4972965034855828</v>
       </c>
       <c r="AA53" s="82">
         <f t="shared" si="71"/>
-        <v>0.37819108573069482</v>
+        <v>0.60730745258009267</v>
       </c>
       <c r="AB53" s="82">
         <f t="shared" si="71"/>
-        <v>0.48969849592413828</v>
+        <v>0.76316771681260465</v>
       </c>
       <c r="AC53" s="82">
         <f t="shared" si="71"/>
-        <v>0.6592937392183339</v>
+        <v>1.0040611271581152</v>
       </c>
       <c r="AD53" s="82">
         <f t="shared" si="71"/>
-        <v>0.91300167549376932</v>
+        <v>1.3618378502961159</v>
       </c>
       <c r="AE53" s="82">
         <f t="shared" si="71"/>
-        <v>1.2785018187525365</v>
+        <v>1.872623030769744</v>
       </c>
       <c r="AF53" s="82">
         <f t="shared" si="71"/>
-        <v>1.7796893328110426</v>
+        <v>2.5695499079547814</v>
       </c>
       <c r="AG53" s="82">
         <f t="shared" si="71"/>
-        <v>2.4721766110241528</v>
+        <v>3.5313090257348927</v>
       </c>
       <c r="AH53" s="82">
         <f t="shared" si="71"/>
-        <v>3.4206667070450631</v>
+        <v>4.8471172220203211</v>
       </c>
     </row>
     <row r="54" spans="2:35">
@@ -16106,43 +16103,43 @@
       </c>
       <c r="Y55" s="82">
         <f>Y45/Y35</f>
-        <v>0.51458150881787723</v>
+        <v>0.44642174662361589</v>
       </c>
       <c r="Z55" s="82">
         <f t="shared" ref="Z55:AH55" si="76">Z45/Z35</f>
-        <v>0.34514357309263943</v>
+        <v>0.53256946852043874</v>
       </c>
       <c r="AA55" s="82">
         <f t="shared" si="76"/>
-        <v>0.42815653144415988</v>
+        <v>0.63631707995108799</v>
       </c>
       <c r="AB55" s="82">
         <f t="shared" si="76"/>
-        <v>0.55546357112793143</v>
+        <v>0.81525933097197423</v>
       </c>
       <c r="AC55" s="82">
         <f t="shared" si="76"/>
-        <v>0.74032905225741719</v>
+        <v>1.0678580708002094</v>
       </c>
       <c r="AD55" s="82">
         <f t="shared" si="76"/>
-        <v>1.0108015917190807</v>
+        <v>1.4371959577813103</v>
       </c>
       <c r="AE55" s="82">
         <f t="shared" si="76"/>
-        <v>1.3779767278149098</v>
+        <v>1.9423918792312567</v>
       </c>
       <c r="AF55" s="82">
         <f t="shared" si="76"/>
-        <v>1.8645548661704905</v>
+        <v>2.6149224125570423</v>
       </c>
       <c r="AG55" s="82">
         <f t="shared" si="76"/>
-        <v>2.5328677804729449</v>
+        <v>3.5390435744481485</v>
       </c>
       <c r="AH55" s="82">
         <f t="shared" si="76"/>
-        <v>3.4443833716928096</v>
+        <v>4.799511360919305</v>
       </c>
     </row>
     <row r="56" spans="2:35" ht="14.25" customHeight="1">
@@ -16185,44 +16182,44 @@
         <v>562.09199999999998</v>
       </c>
       <c r="Y57" s="72">
-        <f>X57+Y45</f>
-        <v>1691.8158842924972</v>
+        <f>SUM(X57:X58)+Y45</f>
+        <v>2836.7628007393587</v>
       </c>
       <c r="Z57" s="72">
         <f t="shared" ref="Z57:AH57" si="79">Y57+Z45</f>
-        <v>2775.5624505991336</v>
+        <v>4538.0275754778804</v>
       </c>
       <c r="AA57" s="72">
         <f t="shared" si="79"/>
-        <v>4535.2287474424884</v>
+        <v>7200.7146349676941</v>
       </c>
       <c r="AB57" s="72">
         <f t="shared" si="79"/>
-        <v>7416.0348987094112</v>
+        <v>11508.354768635189</v>
       </c>
       <c r="AC57" s="72">
         <f t="shared" si="79"/>
-        <v>12079.466729510885</v>
+        <v>18362.521258894085</v>
       </c>
       <c r="AD57" s="72">
         <f t="shared" si="79"/>
-        <v>19568.575385082833</v>
+        <v>29214.549744107564</v>
       </c>
       <c r="AE57" s="72">
         <f t="shared" si="79"/>
-        <v>31379.60529971361</v>
+        <v>46184.232279099611</v>
       </c>
       <c r="AF57" s="72">
         <f t="shared" si="79"/>
-        <v>49790.143038846873</v>
+        <v>72504.0880962261</v>
       </c>
       <c r="AG57" s="72">
         <f t="shared" si="79"/>
-        <v>78357.129383788619</v>
+        <v>113195.30773398418</v>
       </c>
       <c r="AH57" s="72">
         <f t="shared" si="79"/>
-        <v>122541.35699370377</v>
+        <v>175962.10266153057</v>
       </c>
     </row>
     <row r="58" spans="2:35" ht="14.25" customHeight="1">
@@ -16416,7 +16413,7 @@
       </c>
       <c r="Z61" s="52">
         <f>AVERAGE(Y41)*(1-Y54)</f>
-        <v>88.566273092496999</v>
+        <v>-45.196810460641785</v>
       </c>
       <c r="AA61" s="48"/>
       <c r="AB61" s="53">
@@ -16437,7 +16434,7 @@
         <v>122</v>
       </c>
       <c r="AH61" s="51">
-        <v>3.9899999999999998E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="AI61" s="48"/>
     </row>
@@ -16479,7 +16476,7 @@
       </c>
       <c r="Z62" s="54">
         <f>Z61/AE61</f>
-        <v>4.705233090305122E-2</v>
+        <v>-2.4011570175653727E-2</v>
       </c>
       <c r="AA62" s="48"/>
       <c r="AB62" s="48"/>
@@ -16492,7 +16489,7 @@
       </c>
       <c r="AH62" s="51">
         <f>13.4%-AH61</f>
-        <v>9.4100000000000017E-2</v>
+        <v>9.290000000000001E-2</v>
       </c>
       <c r="AI62" s="48"/>
     </row>
@@ -16596,7 +16593,7 @@
       </c>
       <c r="AH64" s="51">
         <f>+AH61+(AH62*AH63)</f>
-        <v>0.25837687834798717</v>
+        <v>0.25679077575481413</v>
       </c>
       <c r="AI64" s="55"/>
     </row>
@@ -16709,7 +16706,7 @@
       </c>
       <c r="AH66" s="53">
         <f>NPV(AH64,Y45:BV45)</f>
-        <v>39550.489853082297</v>
+        <v>56972.130165803392</v>
       </c>
       <c r="AI66" s="55"/>
       <c r="AJ66" s="34"/>
@@ -16786,7 +16783,7 @@
         <v>188.041</v>
       </c>
       <c r="AI67" s="56" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="2:86" ht="14.25" customHeight="1">
@@ -16837,7 +16834,7 @@
       </c>
       <c r="AH68" s="57">
         <f>AH66/AH67</f>
-        <v>210.329076388034</v>
+        <v>302.97717075426846</v>
       </c>
       <c r="AI68" s="79"/>
     </row>
@@ -16889,7 +16886,7 @@
       </c>
       <c r="AH69" s="57">
         <f>Main!C3</f>
-        <v>208.95</v>
+        <v>244.97</v>
       </c>
       <c r="AI69" s="58"/>
     </row>
@@ -16941,7 +16938,7 @@
       </c>
       <c r="AH70" s="51">
         <f>AH68/AH69-1</f>
-        <v>6.6000305720699259E-3</v>
+        <v>0.23679295731831851</v>
       </c>
       <c r="AI70" s="59" t="str">
         <f>IF(AH70&gt;0,"Upside","Downside")</f>
@@ -16986,7 +16983,7 @@
       </c>
       <c r="AG71" s="85" t="str" cm="1">
         <f t="array" ref="AG71">_xlfn.IFS(AH70&gt;=25%,"Strong Buy",AH70&gt;=10.00001%,"Buy",AND(AH70&lt;=10%,AH70&gt;=-4.9999%),"Hold",AND(AH70&lt;=-5%,AH70&gt;=-14.999999%),"Sell",AH70&lt;=-15%,"Strong Sell")</f>
-        <v>Hold</v>
+        <v>Buy</v>
       </c>
       <c r="AH71" s="85"/>
     </row>
@@ -17996,6 +17993,7 @@
   <ignoredErrors>
     <ignoredError sqref="Y10:AH10 X8 W11:X11 I12:K13 C19:L24 C47:L47" evalError="1"/>
     <ignoredError sqref="J77:L79 W84:X85 F77:I78 M77:M78" formulaRange="1"/>
+    <ignoredError sqref="W46:X46" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
